--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H7"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -427,35 +427,40 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>skillName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>skillDescription</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>evolution1Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>evolution2Description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>evolution3Description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>enhancement1Description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>enhancement2Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>enhancement3Description</t>
         </is>
@@ -469,35 +474,40 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
+          <t>반원 베기</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
           <t>전방 반원(사거리 4, 각도 180도) 범위의 적에게 150% 피해를 줍니다.</t>
         </is>
       </c>
-      <c r="C2" t="inlineStr">
+      <c r="D2" t="inlineStr">
         <is>
           <t>공격 판정에 넉백(밀려나는 거리 5, 0.3초)과 기절(3초) 효과가 추가로 부여됩니다.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="E2" t="inlineStr">
         <is>
           <t>공격 범위 안의 적 투사체를 모두 제거합니다.</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>판정이 전방 반원에서 360도 원형으로 바뀌고, 눌러서 최대 3초까지 차징할 수 있습니다. 차징 시간에 비례해 피해가 120%~160%까지 증가합니다.</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>피해량이 55% 증가합니다.</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>재사용 대기시간이 35% 감소합니다.</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>판정 범위가 30% 증가합니다.</t>
         </is>
@@ -511,35 +521,40 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>직선 내려찍기</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
           <t>전방 직선(길이 4, 폭 2) 범위의 적에게 200% 피해를 줍니다.</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="D3" t="inlineStr">
         <is>
           <t>공격 판정에 방어력 감소(30%, 4초)와 기절(3초) 효과가 추가로 부여됩니다.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="E3" t="inlineStr">
         <is>
           <t>판정 범위가 길이 6, 폭 3으로 넓어지고, 맞은 적에게 에어본(1.5초) 효과가 부여됩니다.</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>판정 범위가 길이 2, 폭 1로 좁아지는 대신 피해량이 350%로 크게 증가합니다.</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>피해량이 55% 증가합니다.</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>재사용 대기시간이 35% 감소합니다.</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="I3" t="inlineStr">
         <is>
           <t>판정 범위가 30% 증가합니다.</t>
         </is>
@@ -553,35 +568,40 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>커서 대시</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
           <t>커서 방향으로 짧게(거리 4) 대시로 이동합니다. 피해는 없습니다.</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="D4" t="inlineStr">
         <is>
           <t>대시 시작과 동시에 0.5초간 무적 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="E4" t="inlineStr">
         <is>
           <t>재사용 대기시간 대신 최대 2개의 스택으로 관리됩니다(스택 1개당 4초에 충전).</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>대시가 끝난 직후 4초간 공격력이 20% 증가하는 버프가 부여됩니다.</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>대시 이동 시간이 55% 감소해 더 빠르게 이동합니다.</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>재사용 대기시간이 35% 감소합니다.</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="I4" t="inlineStr">
         <is>
           <t>대시 이동 거리가 30% 증가합니다.</t>
         </is>
@@ -595,35 +615,40 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
+          <t>아크 버스터</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
           <t>정면으로 투사체를 발사해 적과 닿으면 반경 1 범위에 120% 피해를 줍니다. 재사용 대기시간 대신 최대 6개의 스택으로 관리되며(스택 1개당 4초에 충전), 연속 발사는 1초 간격으로 제한됩니다.</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="D5" t="inlineStr">
         <is>
           <t>보유한 스택을 모두 소모해 긴 직선(길이 8, 폭 1) 범위를 즉시 명중시킵니다. 소모한 스택 1개당 피해가 50%씩 증가하며(최대 3스택分까지 적용), 폭발 범위 피해는 없습니다.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
+      <c r="E5" t="inlineStr">
         <is>
           <t>스택 1개로 약화된 투사체(피해 50%)를 0.1초 간격으로 3발 연속 발사합니다. 폭발하지 않고 명중한 대상 하나에게만 피해를 줍니다.</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>스택을 2개 소모해 폭발 반경이 3(기본의 3배)으로 크게 늘어난 확장 폭발탄을 발사합니다. 피해 배율도 250%로 크게 증가합니다.</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>피해량이 55% 증가합니다.</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>스택 충전 시간이 35% 감소합니다.</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
         <is>
           <t>투사체 사거리가 30% 증가합니다.</t>
         </is>
@@ -637,35 +662,40 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
+          <t>폭탄 투척</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
           <t>커서 위치(최대 사거리 6)로 폭탄을 포물선으로 던집니다. 적과 닿거나 착지 후 2초가 지나면 반경 3 범위에 150% 피해를 줍니다.</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>첫 폭발 0.5초 후 반경 4 범위로 2차 폭발이 한 번 더 발생합니다(피해는 첫 폭발의 50%).</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
+      <c r="E6" t="inlineStr">
         <is>
           <t>폭발 반경이 4로 넓어지고, 맞은 적에게 기절(1초)을 겁니다. 폭발 지점에 5초간 유지되는 슬로우 영역이 생겨 안에 있는 적의 이동속도를 40% 감소시킵니다.</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>폭발 범위의 적에게 7초간 마커를 부여합니다. 마커가 걸린 적은 받는 모든 피해가 25% 증가합니다.</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>피해량이 55% 증가합니다.</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>재사용 대기시간이 35% 감소합니다.</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>던질 수 있는 사거리가 30% 증가합니다.</t>
         </is>
@@ -679,35 +709,40 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
+          <t>백스탭 샷</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
           <t>전방 원뿔(사거리 5, 각도 90도) 범위의 적에게 100% 피해를 준 뒤, 커서 반대 방향(후방)으로 짧게(거리 2) 물러납니다.</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="D7" t="inlineStr">
         <is>
           <t>원뿔 공격 대신 처음 위치에 디코이를 설치합니다. 디코이는 3초 후 자동으로 폭발해 반경 3 범위에 100% 피해를 줍니다.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
+      <c r="E7" t="inlineStr">
         <is>
           <t>후방 이동과 동시에 0.3초간 무적 상태가 됩니다.</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>원뿔 공격에 맞은 적을 넉백(밀려나는 거리 3, 0.3초)시킵니다.</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>피해량이 55% 증가합니다.</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>재사용 대기시간이 35% 감소합니다.</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
+      <c r="I7" t="inlineStr">
         <is>
           <t>공격 사거리와 후방 이동 거리가 30% 증가합니다.</t>
         </is>
@@ -724,7 +759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -735,37 +770,324 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>skillName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>skillDescription</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>evolution1Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>evolution2Description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>evolution3Description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>enhancement1Description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>enhancement2Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>enhancement3Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FighterHalfCircleSlash</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Half-Circle Slash</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Deals 150% damage to enemies in a frontal half-circle (range 4, 180°).</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Adds knockback (distance 5, 0.3s) and stun (3s) to the attack.</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Destroys all enemy projectiles within the attack range.</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>The hitbox changes from a frontal half-circle to a full 360° circle, and can be charged for up to 3 seconds by holding the key. Damage increases from 120% to 160% based on charge time.</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>Damage increases by 55%.</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Cooldown decreases by 35%.</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Hitbox size increases by 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FighterLineSlam</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Line Slam</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Deals 200% damage to enemies in a frontal line (length 4, width 2).</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Adds defense reduction (30%, 4s) and stun (3s) to the attack.</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>The hitbox widens to length 6, width 3, and launches hit enemies into the air (1.5s).</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>The hitbox narrows to length 2, width 1, but damage greatly increases to 350%.</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Damage increases by 55%.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Cooldown decreases by 35%.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>Hitbox size increases by 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FighterCursorDash</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cursor Dash</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Dashes a short distance (4) toward the cursor direction. Deals no damage.</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Grants 0.5 seconds of invincibility the moment the dash begins.</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Managed by up to 2 stacks instead of a cooldown (each stack recharges in 4 seconds).</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Immediately after the dash ends, grants a buff that increases attack power by 20% for 4 seconds.</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dash travel time decreases by 55%, moving faster.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Cooldown decreases by 35%.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Dash travel distance increases by 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GunnerArcBuster</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Arc Buster</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Fires a projectile forward that deals 120% damage in a radius of 1 upon contact with an enemy. Managed by up to 6 stacks instead of a cooldown (each stack recharges in 4 seconds), and consecutive shots are limited to a 1-second interval.</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Consumes all held stacks to instantly hit a long line (length 8, width 1). Damage increases by 50% per stack consumed (up to 3 stacks), with no explosion area damage.</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Consumes 1 stack to fire 3 weakened projectiles (50% damage) in succession at 0.1-second intervals. They do not explode and only damage the single target hit.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Consumes 2 stacks to fire an expanded explosive shot with a greatly increased blast radius of 3 (3 times the base). Damage multiplier also greatly increases to 250%.</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Damage increases by 55%.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Stack recharge time decreases by 35%.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Projectile range increases by 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GunnerBombThrow</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Bomb Throw</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Throws a bomb in an arc toward the cursor position (max range 6). Deals 150% damage in a radius of 3 upon contact with an enemy or 2 seconds after landing.</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0.5 seconds after the first explosion, a second explosion occurs once more in a radius of 4 (damage is 50% of the first explosion).</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>The explosion radius widens to 4 and stuns (1s) hit enemies. A slow field that lasts 5 seconds appears at the explosion point, reducing the movement speed of enemies inside by 40%.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Applies a marker to enemies in the explosion range for 7 seconds. Marked enemies take 25% increased damage from all sources.</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Damage increases by 55%.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Cooldown decreases by 35%.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Throw range increases by 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GunnerBackstepShot</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Backstep Shot</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Deals 100% damage to enemies in a frontal cone (range 5, 90°), then steps back a short distance (2) in the direction opposite the cursor.</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Instead of the cone attack, installs a decoy at the original position. The decoy automatically explodes after 3 seconds, dealing 100% damage in a radius of 3.</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Grants 0.3 seconds of invincibility at the same time as the backward movement.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knocks back enemies hit by the cone attack (distance 3, 0.3s).</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Damage increases by 55%.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Cooldown decreases by 35%.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Attack range and backward movement distance increase by 30%.</t>
         </is>
       </c>
     </row>
@@ -780,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,37 +1113,324 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>skillName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>skillDescription</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>evolution1Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>evolution2Description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>evolution3Description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>enhancement1Description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>enhancement2Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>enhancement3Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FighterHalfCircleSlash</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>半円斬り</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>前方の半円範囲（射程4、角度180度）の敵に150%のダメージを与えます。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>攻撃判定にノックバック（距離5、0.3秒）とスタン（3秒）効果が追加されます。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>攻撃範囲内の敵の投射物をすべて除去します。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>判定が前方半円から360度の円形に変わり、押し続けることで最大3秒までチャージできます。チャージ時間に比例してダメージが120%〜160%まで増加します。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ダメージが55%増加します。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>再使用待機時間が35%減少します。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>判定範囲が30%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FighterLineSlam</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>直線叩きつけ</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>前方の直線範囲（長さ4、幅2）の敵に200%のダメージを与えます。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>攻撃判定に防御力減少（30%、4秒）とスタン（3秒）効果が追加されます。</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>判定範囲が長さ6、幅3に広がり、命中した敵にエアボーン(1.5秒)効果が付与されます。</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>判定範囲が長さ2、幅1に狭くなる代わりに、ダメージが350%まで大幅に増加します。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ダメージが55%増加します。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>再使用待機時間が35%減少します。</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>判定範囲が30%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FighterCursorDash</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>カーソルダッシュ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>カーソル方向へ短く（距離4）ダッシュ移動します。ダメージはありません。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>ダッシュ開始と同時に0.5秒間無敵状態になります。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>再使用待機時間の代わりに最大2個のスタックで管理されます（スタック1個につき4秒でチャージ）。</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>ダッシュ終了直後、4秒間攻撃力が20%増加するバフが付与されます。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ダッシュ移動時間が55%減少し、より速く移動します。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>再使用待機時間が35%減少します。</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>ダッシュ移動距離が30%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GunnerArcBuster</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>アークバスター</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>正面に投射物を発射し、敵に命中すると半径1範囲に120%のダメージを与えます。再使用待機時間の代わりに最大6個のスタックで管理され（スタック1個につき4秒でチャージ）、連続発射は1秒間隔に制限されます。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>保有しているスタックをすべて消費し、長い直線（長さ8、幅1）範囲に即座に命中させます。消費したスタック1個につきダメージが50%ずつ増加し（最大3スタック分まで適用）、爆発範囲ダメージはありません。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>スタック1個で弱体化した投射物（ダメージ50%）を0.1秒間隔で3発連続発射します。爆発せず、命中した対象1体にのみダメージを与えます。</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>スタックを2個消費し、爆発半径が3（基本の3倍）まで大幅に広がった拡張爆発弾を発射します。ダメージ倍率も250%まで大幅に増加します。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ダメージが55%増加します。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>スタックチャージ時間が35%減少します。</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>投射物の射程が30%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GunnerBombThrow</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>爆弾投げ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>カーソル位置（最大射程6）へ放物線を描いて爆弾を投げます。敵に接触するか着地後2秒が経過すると、半径3範囲に150%のダメージを与えます。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>最初の爆発から0.5秒後、半径4範囲でもう一度2次爆発が発生します（ダメージは最初の爆発の50%）。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>爆発半径が4に広がり、命中した敵にスタン（1秒）を付与します。爆発地点に5秒間持続するスロー領域が発生し、内部にいる敵の移動速度を40%減少させます。</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>爆発範囲の敵に7秒間マーカーを付与します。マーカーが付いた敵は受けるすべてのダメージが25%増加します。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ダメージが55%増加します。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>再使用待機時間が35%減少します。</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>投げられる射程が30%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GunnerBackstepShot</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>バックステップショット</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>前方円錐（射程5、角度90度）範囲の敵に100%のダメージを与えた後、カーソルの反対方向（後方）へ短く（距離2）後退します。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>円錐攻撃の代わりに元の位置にデコイを設置します。デコイは3秒後に自動的に爆発し、半径3範囲に100%のダメージを与えます。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>後方移動と同時に0.3秒間無敵状態になります。</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>円錐攻撃に命中した敵をノックバック（距離3、0.3秒）させます。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>ダメージが55%増加します。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>再使用待機時間が35%減少します。</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>攻撃射程と後方移動距離が30%増加します。</t>
         </is>
       </c>
     </row>
@@ -836,7 +1445,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H1"/>
+  <dimension ref="A1:I7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -847,37 +1456,324 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
+          <t>skillName</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
           <t>skillDescription</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>evolution1Description</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>evolution2Description</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>evolution3Description</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>enhancement1Description</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="H1" t="inlineStr">
         <is>
           <t>enhancement2Description</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="I1" t="inlineStr">
         <is>
           <t>enhancement3Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>FighterHalfCircleSlash</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>半圆斩</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>对前方半圆范围（射程4，角度180度）内的敌人造成150%伤害。</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>攻击判定额外附加击退（距离5，0.3秒）和眩晕（3秒）效果。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>清除攻击范围内的所有敌方弹幕。</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>判定范围从前方半圆变为360度圆形，可长按最多蓄力3秒。伤害根据蓄力时间从120%增至160%。</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>伤害提高55%。</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>冷却时间减少35%。</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>判定范围扩大30%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>FighterLineSlam</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>直线猛击</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>对前方直线范围（长度4，宽度2）内的敌人造成200%伤害。</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>攻击判定额外附加防御力降低（30%，4秒）和眩晕（3秒）效果。</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>判定范围扩大为长度6、宽度3，命中的敌人会被浮空（1.5秒）。</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>判定范围缩小为长度2、宽度1，但伤害大幅提升至350%。</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>伤害提高55%。</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>冷却时间减少35%。</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>判定范围扩大30%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FighterCursorDash</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>光标冲刺</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>朝光标方向短距离冲刺（距离4）。无伤害。</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>冲刺开始的同时获得0.5秒无敌状态。</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>改为使用最多2层层数管理，不再有冷却时间（每层4秒充能）。</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>冲刺结束后立即获得持续4秒、攻击力提高20%的增益效果。</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>冲刺移动时间减少55%，移动速度更快。</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>冷却时间减少35%。</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>冲刺移动距离增加30%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GunnerArcBuster</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>电弧爆破者</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>向正面发射弹幕，命中敌人时对半径1范围造成120%伤害。改为使用最多6层层数管理，不再有冷却时间（每层4秒充能），连续发射间隔限制为1秒。</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>消耗全部持有层数，立即命中一条长直线范围（长度8，宽度1）。每消耗1层伤害提高50%（最多计算3层），无爆炸范围伤害。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>消耗1层发射3发威力减弱的弹幕（伤害50%），间隔0.1秒连续发射。不会爆炸，只对命中的单个目标造成伤害。</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>消耗2层发射爆炸范围大幅扩大至3（基础的3倍）的扩展爆炸弹。伤害倍率也大幅提升至250%。</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>伤害提高55%。</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>层数充能时间减少35%。</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>弹幕射程增加30%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>GunnerBombThrow</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>投掷炸弹</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>朝光标位置（最大射程6）以抛物线投掷炸弹。接触敌人或落地后2秒，对半径3范围造成150%伤害。</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>首次爆炸0.5秒后，在半径4范围内再发生一次二次爆炸（伤害为首次爆炸的50%）。</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>爆炸范围扩大至4，命中的敌人会被眩晕（1秒）。爆炸点会产生持续5秒的减速区域，使区域内敌人的移动速度降低40%。</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>对爆炸范围内的敌人施加持续7秒的标记。被标记的敌人受到的所有伤害提高25%。</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>伤害提高55%。</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>冷却时间减少35%。</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>投掷射程增加30%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>GunnerBackstepShot</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>后跳射击</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>对前方扇形范围（射程5，角度90度）内的敌人造成100%伤害，随后朝光标反方向（后方）短距离后退（距离2）。</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>不再进行扇形攻击，而是在原位置放置诱饵。诱饵会在3秒后自动爆炸，对半径3范围造成100%伤害。</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>后退移动的同时获得0.3秒无敌状态。</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>扇形攻击命中的敌人会被击退（距离3，0.3秒）。</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>伤害提高55%。</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>冷却时间减少35%。</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>攻击射程和后退移动距离增加30%。</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -745,6 +745,100 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>공격 사거리와 후방 이동 거리가 30% 증가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FighterUltimate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>궁극기(임시)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>전방 반원(사거리 4, 각도 180도) 범위의 적에게 150% 피해를 줍니다.</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>공격 판정에 넉백(밀려나는 거리 5, 0.3초)과 기절(3초) 효과가 추가로 부여됩니다.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>공격 범위 안의 적 투사체를 모두 제거합니다.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>판정이 전방 반원에서 360도 원형으로 바뀌고, 눌러서 최대 3초까지 차징할 수 있습니다. 차징 시간에 비례해 피해가 120%~160%까지 증가합니다.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>피해량이 55% 증가합니다.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>재사용 대기시간이 35% 감소합니다.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>판정 범위가 30% 증가합니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GunnerUltimate</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>궁극기(임시)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>정면으로 투사체를 발사해 적과 닿으면 반경 1 범위에 120% 피해를 줍니다. 재사용 대기시간 대신 최대 6개의 스택으로 관리되며(스택 1개당 4초에 충전), 연속 발사는 1초 간격으로 제한됩니다.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>보유한 스택을 모두 소모해 긴 직선(길이 8, 폭 1) 범위를 즉시 명중시킵니다. 소모한 스택 1개당 피해가 50%씩 증가하며(최대 3스택分까지 적용), 폭발 범위 피해는 없습니다.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>스택 1개로 약화된 투사체(피해 50%)를 0.1초 간격으로 3발 연속 발사합니다. 폭발하지 않고 명중한 대상 하나에게만 피해를 줍니다.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>스택을 2개 소모해 폭발 반경이 3(기본의 3배)으로 크게 늘어난 확장 폭발탄을 발사합니다. 피해 배율도 250%로 크게 증가합니다.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>피해량이 55% 증가합니다.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>스택 충전 시간이 35% 감소합니다.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>투사체 사거리가 30% 증가합니다.</t>
         </is>
       </c>
     </row>
@@ -759,7 +853,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1088,6 +1182,100 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>Attack range and backward movement distance increase by 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FighterUltimate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Ultimate (Temp)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Deals 150% damage to enemies in a frontal half-circle (range 4, 180°).</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Adds knockback (distance 5, 0.3s) and stun (3s) to the attack.</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Destroys all enemy projectiles within the attack range.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>The hitbox changes from a frontal half-circle to a full 360° circle, and can be charged for up to 3 seconds by holding the key. Damage increases from 120% to 160% based on charge time.</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Damage increases by 55%.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Cooldown decreases by 35%.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>Hitbox size increases by 30%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GunnerUltimate</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Ultimate (Temp)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Fires a projectile forward that deals 120% damage in a radius of 1 upon contact with an enemy. Managed by up to 6 stacks instead of a cooldown (each stack recharges in 4 seconds), and consecutive shots are limited to a 1-second interval.</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Consumes all held stacks to instantly hit a long line (length 8, width 1). Damage increases by 50% per stack consumed (up to 3 stacks), with no explosion area damage.</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Consumes 1 stack to fire 3 weakened projectiles (50% damage) in succession at 0.1-second intervals. They do not explode and only damage the single target hit.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Consumes 2 stacks to fire an expanded explosive shot with a greatly increased blast radius of 3 (3 times the base). Damage multiplier also greatly increases to 250%.</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Damage increases by 55%.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Stack recharge time decreases by 35%.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>Projectile range increases by 30%.</t>
         </is>
       </c>
     </row>
@@ -1102,7 +1290,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1431,6 +1619,100 @@
       <c r="I7" t="inlineStr">
         <is>
           <t>攻撃射程と後方移動距離が30%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FighterUltimate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>アルティメット(仮)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>前方の半円範囲（射程4、角度180度）の敵に150%のダメージを与えます。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>攻撃判定にノックバック（距離5、0.3秒）とスタン（3秒）効果が追加されます。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>攻撃範囲内の敵の投射物をすべて除去します。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>判定が前方半円から360度の円形に変わり、押し続けることで最大3秒までチャージできます。チャージ時間に比例してダメージが120%〜160%まで増加します。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ダメージが55%増加します。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>再使用待機時間が35%減少します。</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>判定範囲が30%増加します。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GunnerUltimate</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>アルティメット(仮)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>正面に投射物を発射し、敵に命中すると半径1範囲に120%のダメージを与えます。再使用待機時間の代わりに最大6個のスタックで管理され（スタック1個につき4秒でチャージ）、連続発射は1秒間隔に制限されます。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>保有しているスタックをすべて消費し、長い直線（長さ8、幅1）範囲に即座に命中させます。消費したスタック1個につきダメージが50%ずつ増加し（最大3スタック分まで適用）、爆発範囲ダメージはありません。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>スタック1個で弱体化した投射物（ダメージ50%）を0.1秒間隔で3発連続発射します。爆発せず、命中した対象1体にのみダメージを与えます。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>スタックを2個消費し、爆発半径が3（基本の3倍）まで大幅に広がった拡張爆発弾を発射します。ダメージ倍率も250%まで大幅に増加します。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ダメージが55%増加します。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>スタックチャージ時間が35%減少します。</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>投射物の射程が30%増加します。</t>
         </is>
       </c>
     </row>
@@ -1445,7 +1727,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1777,6 +2059,100 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>FighterUltimate</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>终极技能(临时)</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>对前方半圆范围（射程4，角度180度）内的敌人造成150%伤害。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>攻击判定额外附加击退（距离5，0.3秒）和眩晕（3秒）效果。</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>清除攻击范围内的所有敌方弹幕。</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>判定范围从前方半圆变为360度圆形，可长按最多蓄力3秒。伤害根据蓄力时间从120%增至160%。</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>伤害提高55%。</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>冷却时间减少35%。</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>判定范围扩大30%。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>GunnerUltimate</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>终极技能(临时)</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>向正面发射弹幕，命中敌人时对半径1范围造成120%伤害。改为使用最多6层层数管理，不再有冷却时间（每层4秒充能），连续发射间隔限制为1秒。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>消耗全部持有层数，立即命中一条长直线范围（长度8，宽度1）。每消耗1层伤害提高50%（最多计算3层），无爆炸范围伤害。</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>消耗1层发射3发威力减弱的弹幕（伤害50%），间隔0.1秒连续发射。不会爆炸，只对命中的单个目标造成伤害。</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>消耗2层发射爆炸范围大幅扩大至3（基础的3倍）的扩展爆炸弹。伤害倍率也大幅提升至250%。</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>伤害提高55%。</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>层数充能时间减少35%。</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>弹幕射程增加30%。</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보유한 스택을 모두 소모해 긴 직선(길이 8, 폭 1) 범위를 즉시 명중시킵니다. 소모한 스택 1개당 피해가 50%씩 증가하며(최대 3스택分까지 적용), 폭발 범위 피해는 없습니다.</t>
+          <t>보유한 스택을 모두 소모해 긴 직선(길이 12, 폭 2) 범위를 즉시 명중시킵니다. 소모한 스택 1개당 피해가 50%씩 증가하며(최대 6스택분까지 적용), 폭발 범위 피해는 없습니다.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -756,12 +756,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>궁극기(임시)</t>
+          <t>각성</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>전방 반원(사거리 4, 각도 180도) 범위의 적에게 150% 피해를 줍니다.</t>
+          <t>자신을 중심으로 반경 3 범위의 적에게 100% 피해를 주고, 15초 동안 공격력 30%, 공격 속도 25%, 이동 속도 15%, 방어력 30%가 증가합니다.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>궁극기(임시)</t>
+          <t>융단폭격</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>정면으로 투사체를 발사해 적과 닿으면 반경 1 범위에 120% 피해를 줍니다. 재사용 대기시간 대신 최대 6개의 스택으로 관리되며(스택 1개당 4초에 충전), 연속 발사는 1초 간격으로 제한됩니다.</t>
+          <t>커서 지점을 중심으로 반경 8 영역 전체를 0.5초 간격으로 3번 폭격해, 매번 120% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumes all held stacks to instantly hit a long line (length 8, width 1). Damage increases by 50% per stack consumed (up to 3 stacks), with no explosion area damage.</t>
+          <t>Consumes all stacks to instantly hit a long line (length 12, width 2). Damage increases by 50% per stack consumed (up to 6 stacks). No explosion damage.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Ultimate (Temp)</t>
+          <t>Awakening</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deals 150% damage to enemies in a frontal half-circle (range 4, 180°).</t>
+          <t>Deals 100% damage to enemies within 3 units around you, then increases Attack by 30%, Attack Speed by 25%, Move Speed by 15% and Defense by 30% for 15 seconds.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1240,12 +1240,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Ultimate (Temp)</t>
+          <t>Carpet Bombing</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Fires a projectile forward that deals 120% damage in a radius of 1 upon contact with an enemy. Managed by up to 6 stacks instead of a cooldown (each stack recharges in 4 seconds), and consecutive shots are limited to a 1-second interval.</t>
+          <t>Bombards the entire 8-unit radius area around the cursor 3 times at 0.5s intervals, dealing 120% damage each time.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>保有しているスタックをすべて消費し、長い直線（長さ8、幅1）範囲に即座に命中させます。消費したスタック1個につきダメージが50%ずつ増加し（最大3スタック分まで適用）、爆発範囲ダメージはありません。</t>
+          <t>保有スタックをすべて消費し、長い直線(長さ12、幅2)範囲を即座に命中させます。消費したスタック1個につきダメージが50%ずつ増加し(最大6スタック分まで適用)、爆発範囲ダメージはありません。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>アルティメット(仮)</t>
+          <t>覚醒</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>前方の半円範囲（射程4、角度180度）の敵に150%のダメージを与えます。</t>
+          <t>自分を中心に半径3の範囲の敵に100%ダメージを与え、15秒間 攻撃力が30%、攻撃速度が25%、移動速度が15%、防御力が30%増加します。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1677,12 +1677,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>アルティメット(仮)</t>
+          <t>絨毯爆撃</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>正面に投射物を発射し、敵に命中すると半径1範囲に120%のダメージを与えます。再使用待機時間の代わりに最大6個のスタックで管理され（スタック1個につき4秒でチャージ）、連続発射は1秒間隔に制限されます。</t>
+          <t>カーソル地点を中心に半径8の範囲全体を0.5秒間隔で3回爆撃し、そのたびに120%ダメージを与えます。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>消耗全部持有层数，立即命中一条长直线范围（长度8，宽度1）。每消耗1层伤害提高50%（最多计算3层），无爆炸范围伤害。</t>
+          <t>消耗全部层数，立即命中一条长直线（长度12、宽度2）范围。每消耗1层伤害提升50%（最多计算6层），没有爆炸范围伤害。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2067,12 +2067,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>终极技能(临时)</t>
+          <t>觉醒</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>对前方半圆范围（射程4，角度180度）内的敌人造成150%伤害。</t>
+          <t>对自身周围半径3范围内的敌人造成100%伤害，并在15秒内提升攻击力30%、攻击速度25%、移动速度15%、防御30%。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2114,12 +2114,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>终极技能(临时)</t>
+          <t>地毯式轰炸</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>向正面发射弹幕，命中敌人时对半径1范围造成120%伤害。改为使用最多6层层数管理，不再有冷却时间（每层4秒充能），连续发射间隔限制为1秒。</t>
+          <t>以光标位置为中心，对半径8的整个区域以0.5秒间隔轰炸3次，每次造成120%伤害。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -766,17 +766,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>공격 판정에 넉백(밀려나는 거리 5, 0.3초)과 기절(3초) 효과가 추가로 부여됩니다.</t>
+          <t>시전 폭발은 그대로고, 강화 효과가 공격 속도 50%와 일반공격 피해 50% 증가로 바뀝니다. 대신 공격력 증가는 15%로 줄어듭니다.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>공격 범위 안의 적 투사체를 모두 제거합니다.</t>
+          <t>시전 폭발은 그대로고, 강화 효과가 스킬 재사용 대기시간 25 감소와 스킬 피해 50% 증가로 바뀝니다. 대신 공격력 증가는 15%로 줄어듭니다.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>판정이 전방 반원에서 360도 원형으로 바뀌고, 눌러서 최대 3초까지 차징할 수 있습니다. 차징 시간에 비례해 피해가 120%~160%까지 증가합니다.</t>
+          <t>시전 폭발의 피해가 400%로, 반경이 1.7배로 커집니다. 대신 강화 효과 지속시간이 5초로 줄어듭니다.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1203,17 +1203,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Adds knockback (distance 5, 0.3s) and stun (3s) to the attack.</t>
+          <t>The cast explosion is unchanged, but the buff becomes +50% attack speed and +50% normal attack damage. In exchange, the attack power bonus drops to 15%.</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Destroys all enemy projectiles within the attack range.</t>
+          <t>The cast explosion is unchanged, but the buff becomes 25 cooldown reduction and +50% skill damage. In exchange, the attack power bonus drops to 15%.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The hitbox changes from a frontal half-circle to a full 360° circle, and can be charged for up to 3 seconds by holding the key. Damage increases from 120% to 160% based on charge time.</t>
+          <t>The cast explosion deals 400% damage with 1.7x the radius. In exchange, the buff lasts only 5 seconds.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1640,17 +1640,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>攻撃判定にノックバック（距離5、0.3秒）とスタン（3秒）効果が追加されます。</t>
+          <t>詠唱時の爆発はそのままで、強化効果が攻撃速度50%と通常攻撃ダメージ50%増加に変わります。代わりに攻撃力増加は15%に減ります。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>攻撃範囲内の敵の投射物をすべて除去します。</t>
+          <t>詠唱時の爆発はそのままで、強化効果がスキル再使用待機時間25減少とスキルダメージ50%増加に変わります。代わりに攻撃力増加は15%に減ります。</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>判定が前方半円から360度の円形に変わり、押し続けることで最大3秒までチャージできます。チャージ時間に比例してダメージが120%〜160%まで増加します。</t>
+          <t>詠唱時の爆発ダメージが400%、半径が1.7倍になります。代わりに強化効果の持続時間が5秒に短縮されます。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2077,17 +2077,17 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>攻击判定额外附加击退（距离5，0.3秒）和眩晕（3秒）效果。</t>
+          <t>施放时的爆炸保持不变，强化效果变为攻击速度提升50%和普通攻击伤害提升50%。作为代价，攻击力提升降为15%。</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>清除攻击范围内的所有敌方弹幕。</t>
+          <t>施放时的爆炸保持不变，强化效果变为技能冷却缩减25和技能伤害提升50%。作为代价，攻击力提升降为15%。</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>判定范围从前方半圆变为360度圆形，可长按最多蓄力3秒。伤害根据蓄力时间从120%增至160%。</t>
+          <t>施放时的爆炸伤害提升至400%，半径扩大至1.7倍。作为代价，强化效果持续时间缩短至5秒。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -813,17 +813,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>보유한 스택을 모두 소모해 긴 직선(길이 8, 폭 1) 범위를 즉시 명중시킵니다. 소모한 스택 1개당 피해가 50%씩 증가하며(최대 3스택分까지 적용), 폭발 범위 피해는 없습니다.</t>
+          <t>회당 피해가 90%로 줄어드는 대신, 15초 동안 공격 속도 50%와 일반공격 피해 50%가 증가하는 효과를 얻습니다.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>스택 1개로 약화된 투사체(피해 50%)를 0.1초 간격으로 3발 연속 발사합니다. 폭발하지 않고 명중한 대상 하나에게만 피해를 줍니다.</t>
+          <t>회당 피해가 90%로 줄어드는 대신, 15초 동안 스킬 재사용 대기시간이 25 감소하고 스킬 피해가 50% 증가하는 효과를 얻습니다.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>스택을 2개 소모해 폭발 반경이 3(기본의 3배)으로 크게 늘어난 확장 폭발탄을 발사합니다. 피해 배율도 250%로 크게 증가합니다.</t>
+          <t>3번에 나눠 폭격하는 대신 단 한 번에 500% 피해를 줍니다. 대신 폭격 반경이 5로 좁아집니다.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Consumes all held stacks to instantly hit a long line (length 8, width 1). Damage increases by 50% per stack consumed (up to 3 stacks), with no explosion area damage.</t>
+          <t>Damage per wave drops to 90%, but you gain +50% attack speed and +50% normal attack damage for 15 seconds.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Consumes 1 stack to fire 3 weakened projectiles (50% damage) in succession at 0.1-second intervals. They do not explode and only damage the single target hit.</t>
+          <t>Damage per wave drops to 90%, but you gain 25 cooldown reduction and +50% skill damage for 15 seconds.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Consumes 2 stacks to fire an expanded explosive shot with a greatly increased blast radius of 3 (3 times the base). Damage multiplier also greatly increases to 250%.</t>
+          <t>Instead of three waves, a single strike deals 500% damage. In exchange, the bombardment radius narrows to 5.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>保有しているスタックをすべて消費し、長い直線（長さ8、幅1）範囲に即座に命中させます。消費したスタック1個につきダメージが50%ずつ増加し（最大3スタック分まで適用）、爆発範囲ダメージはありません。</t>
+          <t>1回あたりのダメージが90%に減る代わりに、15秒間攻撃速度50%と通常攻撃ダメージ50%が上昇します。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>スタック1個で弱体化した投射物（ダメージ50%）を0.1秒間隔で3発連続発射します。爆発せず、命中した対象1体にのみダメージを与えます。</t>
+          <t>1回あたりのダメージが90%に減る代わりに、15秒間スキル再使用待機時間25減少とスキルダメージ50%上昇を得ます。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>スタックを2個消費し、爆発半径が3（基本の3倍）まで大幅に広がった拡張爆発弾を発射します。ダメージ倍率も250%まで大幅に増加します。</t>
+          <t>3回に分けず、一度に500%のダメージを与えます。代わりに爆撃半径が5に狭まります。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>消耗全部持有层数，立即命中一条长直线范围（长度8，宽度1）。每消耗1层伤害提高50%（最多计算3层），无爆炸范围伤害。</t>
+          <t>每波伤害降为90%，但可获得15秒内攻击速度提升50%和普通攻击伤害提升50%。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>消耗1层发射3发威力减弱的弹幕（伤害50%），间隔0.1秒连续发射。不会爆炸，只对命中的单个目标造成伤害。</t>
+          <t>每波伤害降为90%，但可获得15秒内技能冷却缩减25和技能伤害提升50%。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>消耗2层发射爆炸范围大幅扩大至3（基础的3倍）的扩展爆炸弹。伤害倍率也大幅提升至250%。</t>
+          <t>不再分三波轰炸，而是一次造成500%伤害。作为代价，轰炸半径缩小至5。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -813,17 +813,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>회당 피해가 90%로 줄어드는 대신, 15초 동안 공격 속도 50%와 일반공격 피해 50%가 증가하는 효과를 얻습니다.</t>
+          <t>여러 번 나눠 폭격하는 대신, 시전 0.5초 뒤 영역 전체에 360% 피해를 단 한 번에 줍니다.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>회당 피해가 90%로 줄어드는 대신, 15초 동안 스킬 재사용 대기시간이 25 감소하고 스킬 피해가 50% 증가하는 효과를 얻습니다.</t>
+          <t>폭격 횟수가 4회로 늘어나고 회당 피해는 90%가 됩니다. 폭격에 적중된 적은 6초 동안 받는 모든 피해가 25% 증가합니다.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3번에 나눠 폭격하는 대신 단 한 번에 500% 피해를 줍니다. 대신 폭격 반경이 5로 좁아집니다.</t>
+          <t>영역 전체 폭격 대신, 범위 안 랜덤한 위치에 고위력 포탄을 0.3초 간격으로 9발 떨어뜨립니다. 포탄 한 발은 반경 2 범위에 200% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Damage per wave drops to 90%, but you gain +50% attack speed and +50% normal attack damage for 15 seconds.</t>
+          <t>Instead of several waves, a single strike hits the whole area for 360% damage 0.5 seconds after casting.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Damage per wave drops to 90%, but you gain 25 cooldown reduction and +50% skill damage for 15 seconds.</t>
+          <t>The bombardment runs 4 waves at 90% damage each. Enemies hit are marked for 6 seconds, taking 25% increased damage from all sources.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Instead of three waves, a single strike deals 500% damage. In exchange, the bombardment radius narrows to 5.</t>
+          <t>Instead of blanketing the area, nine high-power shells land at random points 0.3 seconds apart. Each shell deals 200% damage in a radius of 2.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>1回あたりのダメージが90%に減る代わりに、15秒間攻撃速度50%と通常攻撃ダメージ50%が上昇します。</t>
+          <t>何度も分けて爆撃する代わりに、詠唱の0.5秒後に領域全体へ360%のダメージを一度で与えます。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1回あたりのダメージが90%に減る代わりに、15秒間スキル再使用待機時間25減少とスキルダメージ50%上昇を得ます。</t>
+          <t>爆撃回数が4回になり、1回あたりのダメージは90%になります。命中した敵は6秒間、受けるダメージが25%増加します。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3回に分けず、一度に500%のダメージを与えます。代わりに爆撃半径が5に狭まります。</t>
+          <t>領域全体への爆撃の代わりに、範囲内のランダムな位置へ高威力砲弾を0.3秒間隔で9発落とします。砲弾1発は半径2の範囲に200%のダメージを与えます。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>每波伤害降为90%，但可获得15秒内攻击速度提升50%和普通攻击伤害提升50%。</t>
+          <t>不再分多波轰炸，而是在施放0.5秒后对整个区域一次性造成360%伤害。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>每波伤害降为90%，但可获得15秒内技能冷却缩减25和技能伤害提升50%。</t>
+          <t>轰炸次数增加至4次，每波伤害变为90%。被命中的敌人在6秒内受到的所有伤害提升25%。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>不再分三波轰炸，而是一次造成500%伤害。作为代价，轰炸半径缩小至5。</t>
+          <t>不再覆盖整个区域，而是以0.3秒间隔向范围内的随机位置投下9发高威力炮弹。每发炮弹对半径2的范围造成200%伤害。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -813,17 +813,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>여러 번 나눠 폭격하는 대신, 시전 0.5초 뒤 영역 전체에 360% 피해를 단 한 번에 줍니다.</t>
+          <t>여러 번 나눠 폭격하는 대신, 시전 0.5초 뒤 영역 전체에 450% 피해를 단 한 번에 줍니다.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>폭격 횟수가 4회로 늘어나고 회당 피해는 90%가 됩니다. 폭격에 적중된 적은 6초 동안 받는 모든 피해가 25% 증가합니다.</t>
+          <t>폭격이 1초 간격으로 4회 이어지며 회당 100% 피해를 줍니다. 적중된 적은 5초 동안 받는 모든 피해가 25% 증가하며, 다시 적중하면 남은 시간에 더해집니다.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>영역 전체 폭격 대신, 범위 안 랜덤한 위치에 고위력 포탄을 0.3초 간격으로 9발 떨어뜨립니다. 포탄 한 발은 반경 2 범위에 200% 피해를 줍니다.</t>
+          <t>영역 전체 폭격 대신, 범위 안 랜덤한 위치에 포탄을 0.3초 간격으로 9발 떨어뜨립니다. 포탄 한 발은 반경 3 범위에 60% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1250,17 +1250,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Instead of several waves, a single strike hits the whole area for 360% damage 0.5 seconds after casting.</t>
+          <t>Instead of several waves, a single strike hits the whole area for 450% damage 0.5 seconds after casting.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The bombardment runs 4 waves at 90% damage each. Enemies hit are marked for 6 seconds, taking 25% increased damage from all sources.</t>
+          <t>The bombardment runs 4 waves one second apart, dealing 100% damage each. Enemies hit are marked for 5 seconds, taking 25% increased damage from all sources; hitting them again adds to the remaining duration.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Instead of blanketing the area, nine high-power shells land at random points 0.3 seconds apart. Each shell deals 200% damage in a radius of 2.</t>
+          <t>Instead of blanketing the area, nine shells land at random points 0.3 seconds apart. Each shell deals 60% damage in a radius of 3.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1687,17 +1687,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>何度も分けて爆撃する代わりに、詠唱の0.5秒後に領域全体へ360%のダメージを一度で与えます。</t>
+          <t>何度も分けて爆撃する代わりに、詠唱の0.5秒後に領域全体へ450%のダメージを一度で与えます。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>爆撃回数が4回になり、1回あたりのダメージは90%になります。命中した敵は6秒間、受けるダメージが25%増加します。</t>
+          <t>爆撃が1秒間隔で4回続き、1回あたり100%のダメージを与えます。命中した敵は5秒間受けるダメージが25%増加し、再度命中すると残り時間に加算されます。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>領域全体への爆撃の代わりに、範囲内のランダムな位置へ高威力砲弾を0.3秒間隔で9発落とします。砲弾1発は半径2の範囲に200%のダメージを与えます。</t>
+          <t>領域全体への爆撃の代わりに、範囲内のランダムな位置へ砲弾を0.3秒間隔で9発落とします。砲弾1発は半径3の範囲に60%のダメージを与えます。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -2124,17 +2124,17 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>不再分多波轰炸，而是在施放0.5秒后对整个区域一次性造成360%伤害。</t>
+          <t>不再分多波轰炸，而是在施放0.5秒后对整个区域一次性造成450%伤害。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>轰炸次数增加至4次，每波伤害变为90%。被命中的敌人在6秒内受到的所有伤害提升25%。</t>
+          <t>轰炸以1秒间隔进行4波，每波造成100%伤害。被命中的敌人在5秒内受到的所有伤害提升25%，再次命中时会叠加剩余时间。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>不再覆盖整个区域，而是以0.3秒间隔向范围内的随机位置投下9发高威力炮弹。每发炮弹对半径2的范围造成200%伤害。</t>
+          <t>不再覆盖整个区域，而是以0.3秒间隔向范围内的随机位置投下9发炮弹。每发炮弹对半径3的范围造成60%伤害。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -625,7 +625,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>보유한 스택을 모두 소모해 긴 직선(길이 12, 폭 2) 범위를 즉시 명중시킵니다. 소모한 스택 1개당 피해가 50%씩 증가하며(최대 6스택분까지 적용), 폭발 범위 피해는 없습니다.</t>
+          <t>스택을 소모해 긴 직선(길이 12, 폭 2)을 즉시 명중시킵니다. 스택 1개당 MP 35를 쓰며, MP가 부족하면 가능한 만큼만 소모합니다. 소모한 스택당 피해 +50%(최대 6스택), 폭발 피해는 없습니다.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumes all stacks to instantly hit a long line (length 12, width 2). Damage increases by 50% per stack consumed (up to 6 stacks). No explosion damage.</t>
+          <t>Consumes stacks to instantly hit a long line (length 12, width 2). 35 MP per stack (only as many as MP allows). +50% damage per stack (max 6). No explosion.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1499,7 +1499,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>保有スタックをすべて消費し、長い直線(長さ12、幅2)範囲を即座に命中させます。消費したスタック1個につきダメージが50%ずつ増加し(最大6スタック分まで適用)、爆発範囲ダメージはありません。</t>
+          <t>スタックを消費し、長い直線(長さ12、幅2)を即座に攻撃。1スタックにつきMP35を消費(MP不足時は可能な分のみ)。1スタックにつきダメージ+50%(最大6)、爆発なし。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>消耗全部层数，立即命中一条长直线（长度12、宽度2）范围。每消耗1层伤害提升50%（最多计算6层），没有爆炸范围伤害。</t>
+          <t>消耗层数，立即命中一条长直线（长度12、宽度2）。每层消耗35点MP，MP不足时只消耗可支付的层数。每层伤害+50%（最多6层），无爆炸伤害。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -823,22 +823,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>영역 전체 폭격 대신, 범위 안 랜덤한 위치에 포탄을 0.3초 간격으로 9발 떨어뜨립니다. 포탄 한 발은 반경 3 범위에 60% 피해를 줍니다.</t>
+          <t>영역 전체 폭격 대신, 범위 안 랜덤한 위치에 포탄을 0.35초 간격으로 9발 떨어뜨립니다. 포탄 한 발은 반경 3 범위에 60% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>피해량이 55% 증가합니다.</t>
+          <t>피해량이 15% 증가합니다.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>스택 충전 시간이 35% 감소합니다.</t>
+          <t>쿨다운이 15% 감소합니다.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>투사체 사거리가 30% 증가합니다.</t>
+          <t>지정 거리와 산탄 폭발 반경이 각각 15% 증가합니다.</t>
         </is>
       </c>
     </row>
@@ -1260,22 +1260,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Instead of blanketing the area, nine shells land at random points 0.3 seconds apart. Each shell deals 60% damage in a radius of 3.</t>
+          <t>Instead of blanketing the area, nine shells land at random points 0.35 seconds apart. Each shell deals 60% damage in a radius of 3.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Damage increases by 55%.</t>
+          <t>Damage increases by 15%.</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Stack recharge time decreases by 35%.</t>
+          <t>Cooldown decreases by 15%.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Projectile range increases by 30%.</t>
+          <t>Targeting distance and each barrage shell's explosion radius increase by 15%.</t>
         </is>
       </c>
     </row>
@@ -1697,22 +1697,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>領域全体への爆撃の代わりに、範囲内のランダムな位置へ砲弾を0.3秒間隔で9発落とします。砲弾1発は半径3の範囲に60%のダメージを与えます。</t>
+          <t>領域全体への爆撃の代わりに、範囲内のランダムな位置へ砲弾を0.35秒間隔で9発落とします。砲弾1発は半径3の範囲に60%のダメージを与えます。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>ダメージが55%増加します。</t>
+          <t>ダメージが15%増加します。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>スタックチャージ時間が35%減少します。</t>
+          <t>クールダウンが15%減少します。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>投射物の射程が30%増加します。</t>
+          <t>指定距離と散弾爆撃の砲弾の爆発半径がそれぞれ15%増加します。</t>
         </is>
       </c>
     </row>
@@ -2134,22 +2134,22 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>不再覆盖整个区域，而是以0.3秒间隔向范围内的随机位置投下9发炮弹。每发炮弹对半径3的范围造成60%伤害。</t>
+          <t>不再覆盖整个区域，而是以0.35秒间隔向范围内的随机位置投下9发炮弹。每发炮弹对半径3的范围造成60%伤害。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>伤害提高55%。</t>
+          <t>伤害提高15%。</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>层数充能时间减少35%。</t>
+          <t>冷却时间减少15%。</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>弹幕射程增加30%。</t>
+          <t>指定距离和散弹轰炸中每发炮弹的爆炸半径各增加15%。</t>
         </is>
       </c>
     </row>

--- a/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
+++ b/Assets/Resources/DataFiles/CharData/SkillData/1. ExcelFile/SkillDataLabel.xlsx
@@ -479,7 +479,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>전방 반원(사거리 4, 각도 180도) 범위의 적에게 150% 피해를 줍니다.</t>
+          <t>전방 반원(사거리 4, 각도 180도) 범위의 적에게 270% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>판정이 전방 반원에서 360도 원형으로 바뀌고, 눌러서 최대 3초까지 차징할 수 있습니다. 차징 시간에 비례해 피해가 120%~160%까지 증가합니다.</t>
+          <t>판정이 전방 반원에서 360도 원형으로 바뀌고, 눌러서 최대 3초까지 차징할 수 있습니다. 차징 시간에 비례해 피해가 270%~470%까지 증가합니다.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -526,7 +526,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>전방 직선(길이 4, 폭 2) 범위의 적에게 200% 피해를 줍니다.</t>
+          <t>전방 직선(길이 4, 폭 2) 범위의 적에게 360% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>판정 범위가 길이 2, 폭 1로 좁아지는 대신 피해량이 350%로 크게 증가합니다.</t>
+          <t>판정 범위가 길이 2, 폭 1로 좁아지는 대신 피해량이 630%로 크게 증가합니다.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -620,22 +620,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>정면으로 투사체를 발사해 적과 닿으면 반경 1 범위에 120% 피해를 줍니다. 재사용 대기시간 대신 최대 6개의 스택으로 관리되며(스택 1개당 4초에 충전), 연속 발사는 1초 간격으로 제한됩니다.</t>
+          <t>정면으로 투사체를 발사해 적과 닿으면 반경 1 범위에 216% 피해를 줍니다. 재사용 대기시간 대신 최대 6개의 스택으로 관리되며(스택 1개당 4초에 충전), 연속 발사는 1초 간격으로 제한됩니다.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>스택을 소모해 긴 직선(길이 12, 폭 2)을 즉시 명중시킵니다. 스택 1개당 MP 35를 쓰며, MP가 부족하면 가능한 만큼만 소모합니다. 소모한 스택당 피해 +50%(최대 6스택), 폭발 피해는 없습니다.</t>
+          <t>스택을 소모해 긴 직선(길이 12, 폭 2)을 즉시 명중시킵니다. 스택 1개당 MP 27를 쓰며, MP가 부족하면 가능한 만큼만 소모합니다. 소모한 스택당 피해 +50%(최대 6스택), 폭발 피해는 없습니다.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>스택 1개로 약화된 투사체(피해 50%)를 0.1초 간격으로 3발 연속 발사합니다. 폭발하지 않고 명중한 대상 하나에게만 피해를 줍니다.</t>
+          <t>스택 1개로 약화된 투사체(피해 90%)를 0.1초 간격으로 3발 연속 발사합니다. 폭발하지 않고 명중한 대상 하나에게만 피해를 줍니다.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>스택을 2개 소모해 폭발 반경이 3(기본의 3배)으로 크게 늘어난 확장 폭발탄을 발사합니다. 피해 배율도 250%로 크게 증가합니다.</t>
+          <t>스택을 2개 소모해 폭발 반경이 3(기본의 3배)으로 크게 늘어난 확장 폭발탄을 발사합니다. 피해 배율도 450%로 크게 증가합니다.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -667,7 +667,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>커서 위치(최대 사거리 6)로 폭탄을 포물선으로 던집니다. 적과 닿거나 착지 후 2초가 지나면 반경 3 범위에 150% 피해를 줍니다.</t>
+          <t>커서 위치(최대 사거리 6)로 폭탄을 포물선으로 던집니다. 적과 닿거나 착지 후 2초가 지나면 반경 3 범위에 270% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -714,12 +714,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>전방 원뿔(사거리 5, 각도 90도) 범위의 적에게 100% 피해를 준 뒤, 커서 반대 방향(후방)으로 짧게(거리 2) 물러납니다.</t>
+          <t>전방 원뿔(사거리 5, 각도 90도) 범위의 적에게 180% 피해를 준 뒤, 커서 반대 방향(후방)으로 짧게(거리 2) 물러납니다.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>원뿔 공격 대신 처음 위치에 디코이를 설치합니다. 디코이는 3초 후 자동으로 폭발해 반경 3 범위에 100% 피해를 줍니다.</t>
+          <t>원뿔 공격 대신 처음 위치에 디코이를 설치합니다. 디코이는 3초 후 자동으로 폭발해 반경 3 범위에 180% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -761,7 +761,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>자신을 중심으로 반경 3 범위의 적에게 100% 피해를 주고, 15초 동안 공격력 30%, 공격 속도 25%, 이동 속도 15%, 방어력 30%가 증가합니다.</t>
+          <t>자신을 중심으로 반경 3 범위의 적에게 180% 피해를 주고, 15초 동안 공격력 30%, 공격 속도 25%, 이동 속도 15%, 방어력 30%가 증가합니다.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>시전 폭발의 피해가 400%로, 반경이 1.7배로 커집니다. 대신 강화 효과 지속시간이 5초로 줄어듭니다.</t>
+          <t>시전 폭발의 피해가 720%로, 반경이 1.7배로 커집니다. 대신 강화 효과 지속시간이 5초로 줄어듭니다.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -808,22 +808,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>커서 지점을 중심으로 반경 8 영역 전체를 0.5초 간격으로 3번 폭격해, 매번 120% 피해를 줍니다.</t>
+          <t>커서 지점을 중심으로 반경 8 영역 전체를 0.5초 간격으로 3번 폭격해, 매번 216% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>여러 번 나눠 폭격하는 대신, 시전 0.5초 뒤 영역 전체에 450% 피해를 단 한 번에 줍니다.</t>
+          <t>여러 번 나눠 폭격하는 대신, 시전 0.5초 뒤 영역 전체에 810% 피해를 단 한 번에 줍니다.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>폭격이 1초 간격으로 4회 이어지며 회당 100% 피해를 줍니다. 적중된 적은 5초 동안 받는 모든 피해가 25% 증가하며, 다시 적중하면 남은 시간에 더해집니다.</t>
+          <t>폭격이 1초 간격으로 4회 이어지며 회당 180% 피해를 줍니다. 적중된 적은 5초 동안 받는 모든 피해가 25% 증가하며, 다시 적중하면 남은 시간에 더해집니다.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>영역 전체 폭격 대신, 범위 안 랜덤한 위치에 포탄을 0.35초 간격으로 9발 떨어뜨립니다. 포탄 한 발은 반경 3 범위에 60% 피해를 줍니다.</t>
+          <t>영역 전체 폭격 대신, 범위 안 랜덤한 위치에 포탄을 0.35초 간격으로 9발 떨어뜨립니다. 포탄 한 발은 반경 3 범위에 108% 피해를 줍니다.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Deals 150% damage to enemies in a frontal half-circle (range 4, 180°).</t>
+          <t>Deals 270% damage to enemies in a frontal half-circle (range 4, 180°).</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -931,7 +931,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>The hitbox changes from a frontal half-circle to a full 360° circle, and can be charged for up to 3 seconds by holding the key. Damage increases from 120% to 160% based on charge time.</t>
+          <t>The hitbox changes from a frontal half-circle to a full 360° circle, and can be charged for up to 3 seconds by holding the key. Damage increases from 270% to 470% based on charge time.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -963,7 +963,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Deals 200% damage to enemies in a frontal line (length 4, width 2).</t>
+          <t>Deals 360% damage to enemies in a frontal line (length 4, width 2).</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>The hitbox narrows to length 2, width 1, but damage greatly increases to 350%.</t>
+          <t>The hitbox narrows to length 2, width 1, but damage greatly increases to 630%.</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1057,22 +1057,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fires a projectile forward that deals 120% damage in a radius of 1 upon contact with an enemy. Managed by up to 6 stacks instead of a cooldown (each stack recharges in 4 seconds), and consecutive shots are limited to a 1-second interval.</t>
+          <t>Fires a projectile forward that deals 216% damage in a radius of 1 upon contact with an enemy. Managed by up to 6 stacks instead of a cooldown (each stack recharges in 4 seconds), and consecutive shots are limited to a 1-second interval.</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Consumes stacks to instantly hit a long line (length 12, width 2). 35 MP per stack (only as many as MP allows). +50% damage per stack (max 6). No explosion.</t>
+          <t>Consumes stacks to instantly hit a long line (length 12, width 2). 27 MP per stack (only as many as MP allows). +50% damage per stack (max 6). No explosion.</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Consumes 1 stack to fire 3 weakened projectiles (50% damage) in succession at 0.1-second intervals. They do not explode and only damage the single target hit.</t>
+          <t>Consumes 1 stack to fire 3 weakened projectiles (90% damage) in succession at 0.1-second intervals. They do not explode and only damage the single target hit.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Consumes 2 stacks to fire an expanded explosive shot with a greatly increased blast radius of 3 (3 times the base). Damage multiplier also greatly increases to 250%.</t>
+          <t>Consumes 2 stacks to fire an expanded explosive shot with a greatly increased blast radius of 3 (3 times the base). Damage multiplier also greatly increases to 450%.</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Throws a bomb in an arc toward the cursor position (max range 6). Deals 150% damage in a radius of 3 upon contact with an enemy or 2 seconds after landing.</t>
+          <t>Throws a bomb in an arc toward the cursor position (max range 6). Deals 270% damage in a radius of 3 upon contact with an enemy or 2 seconds after landing.</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1151,12 +1151,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Deals 100% damage to enemies in a frontal cone (range 5, 90°), then steps back a short distance (2) in the direction opposite the cursor.</t>
+          <t>Deals 180% damage to enemies in a frontal cone (range 5, 90°), then steps back a short distance (2) in the direction opposite the cursor.</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Instead of the cone attack, installs a decoy at the original position. The decoy automatically explodes after 3 seconds, dealing 100% damage in a radius of 3.</t>
+          <t>Instead of the cone attack, installs a decoy at the original position. The decoy automatically explodes after 3 seconds, dealing 180% damage in a radius of 3.</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Deals 100% damage to enemies within 3 units around you, then increases Attack by 30%, Attack Speed by 25%, Move Speed by 15% and Defense by 30% for 15 seconds.</t>
+          <t>Deals 180% damage to enemies within 3 units around you, then increases Attack by 30%, Attack Speed by 25%, Move Speed by 15% and Defense by 30% for 15 seconds.</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>The cast explosion deals 400% damage with 1.7x the radius. In exchange, the buff lasts only 5 seconds.</t>
+          <t>The cast explosion deals 720% damage with 1.7x the radius. In exchange, the buff lasts only 5 seconds.</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1245,22 +1245,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Bombards the entire 8-unit radius area around the cursor 3 times at 0.5s intervals, dealing 120% damage each time.</t>
+          <t>Bombards the entire 8-unit radius area around the cursor 3 times at 0.5s intervals, dealing 216% damage each time.</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Instead of several waves, a single strike hits the whole area for 450% damage 0.5 seconds after casting.</t>
+          <t>Instead of several waves, a single strike hits the whole area for 810% damage 0.5 seconds after casting.</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>The bombardment runs 4 waves one second apart, dealing 100% damage each. Enemies hit are marked for 5 seconds, taking 25% increased damage from all sources; hitting them again adds to the remaining duration.</t>
+          <t>The bombardment runs 4 waves one second apart, dealing 180% damage each. Enemies hit are marked for 5 seconds, taking 25% increased damage from all sources; hitting them again adds to the remaining duration.</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Instead of blanketing the area, nine shells land at random points 0.35 seconds apart. Each shell deals 60% damage in a radius of 3.</t>
+          <t>Instead of blanketing the area, nine shells land at random points 0.35 seconds apart. Each shell deals 108% damage in a radius of 3.</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>前方の半円範囲（射程4、角度180度）の敵に150%のダメージを与えます。</t>
+          <t>前方の半円範囲（射程4、角度180度）の敵に270%のダメージを与えます。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>判定が前方半円から360度の円形に変わり、押し続けることで最大3秒までチャージできます。チャージ時間に比例してダメージが120%〜160%まで増加します。</t>
+          <t>判定が前方半円から360度の円形に変わり、押し続けることで最大3秒までチャージできます。チャージ時間に比例してダメージが270%〜470%まで増加します。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>前方の直線範囲（長さ4、幅2）の敵に200%のダメージを与えます。</t>
+          <t>前方の直線範囲（長さ4、幅2）の敵に360%のダメージを与えます。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1415,7 +1415,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>判定範囲が長さ2、幅1に狭くなる代わりに、ダメージが350%まで大幅に増加します。</t>
+          <t>判定範囲が長さ2、幅1に狭くなる代わりに、ダメージが630%まで大幅に増加します。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1494,22 +1494,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>正面に投射物を発射し、敵に命中すると半径1範囲に120%のダメージを与えます。再使用待機時間の代わりに最大6個のスタックで管理され（スタック1個につき4秒でチャージ）、連続発射は1秒間隔に制限されます。</t>
+          <t>正面に投射物を発射し、敵に命中すると半径1範囲に216%のダメージを与えます。再使用待機時間の代わりに最大6個のスタックで管理され（スタック1個につき4秒でチャージ）、連続発射は1秒間隔に制限されます。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>スタックを消費し、長い直線(長さ12、幅2)を即座に攻撃。1スタックにつきMP35を消費(MP不足時は可能な分のみ)。1スタックにつきダメージ+50%(最大6)、爆発なし。</t>
+          <t>スタックを消費し、長い直線(長さ12、幅2)を即座に攻撃。1スタックにつきMP27を消費(MP不足時は可能な分のみ)。1スタックにつきダメージ+50%(最大6)、爆発なし。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>スタック1個で弱体化した投射物（ダメージ50%）を0.1秒間隔で3発連続発射します。爆発せず、命中した対象1体にのみダメージを与えます。</t>
+          <t>スタック1個で弱体化した投射物（ダメージ90%）を0.1秒間隔で3発連続発射します。爆発せず、命中した対象1体にのみダメージを与えます。</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>スタックを2個消費し、爆発半径が3（基本の3倍）まで大幅に広がった拡張爆発弾を発射します。ダメージ倍率も250%まで大幅に増加します。</t>
+          <t>スタックを2個消費し、爆発半径が3（基本の3倍）まで大幅に広がった拡張爆発弾を発射します。ダメージ倍率も450%まで大幅に増加します。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1541,7 +1541,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>カーソル位置（最大射程6）へ放物線を描いて爆弾を投げます。敵に接触するか着地後2秒が経過すると、半径3範囲に150%のダメージを与えます。</t>
+          <t>カーソル位置（最大射程6）へ放物線を描いて爆弾を投げます。敵に接触するか着地後2秒が経過すると、半径3範囲に270%のダメージを与えます。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1588,12 +1588,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>前方円錐（射程5、角度90度）範囲の敵に100%のダメージを与えた後、カーソルの反対方向（後方）へ短く（距離2）後退します。</t>
+          <t>前方円錐（射程5、角度90度）範囲の敵に180%のダメージを与えた後、カーソルの反対方向（後方）へ短く（距離2）後退します。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>円錐攻撃の代わりに元の位置にデコイを設置します。デコイは3秒後に自動的に爆発し、半径3範囲に100%のダメージを与えます。</t>
+          <t>円錐攻撃の代わりに元の位置にデコイを設置します。デコイは3秒後に自動的に爆発し、半径3範囲に180%のダメージを与えます。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>自分を中心に半径3の範囲の敵に100%ダメージを与え、15秒間 攻撃力が30%、攻撃速度が25%、移動速度が15%、防御力が30%増加します。</t>
+          <t>自分を中心に半径3の範囲の敵に180%ダメージを与え、15秒間 攻撃力が30%、攻撃速度が25%、移動速度が15%、防御力が30%増加します。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>詠唱時の爆発ダメージが400%、半径が1.7倍になります。代わりに強化効果の持続時間が5秒に短縮されます。</t>
+          <t>詠唱時の爆発ダメージが720%、半径が1.7倍になります。代わりに強化効果の持続時間が5秒に短縮されます。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -1682,22 +1682,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>カーソル地点を中心に半径8の範囲全体を0.5秒間隔で3回爆撃し、そのたびに120%ダメージを与えます。</t>
+          <t>カーソル地点を中心に半径8の範囲全体を0.5秒間隔で3回爆撃し、そのたびに216%ダメージを与えます。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>何度も分けて爆撃する代わりに、詠唱の0.5秒後に領域全体へ450%のダメージを一度で与えます。</t>
+          <t>何度も分けて爆撃する代わりに、詠唱の0.5秒後に領域全体へ810%のダメージを一度で与えます。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>爆撃が1秒間隔で4回続き、1回あたり100%のダメージを与えます。命中した敵は5秒間受けるダメージが25%増加し、再度命中すると残り時間に加算されます。</t>
+          <t>爆撃が1秒間隔で4回続き、1回あたり180%のダメージを与えます。命中した敵は5秒間受けるダメージが25%増加し、再度命中すると残り時間に加算されます。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>領域全体への爆撃の代わりに、範囲内のランダムな位置へ砲弾を0.35秒間隔で9発落とします。砲弾1発は半径3の範囲に60%のダメージを与えます。</t>
+          <t>領域全体への爆撃の代わりに、範囲内のランダムな位置へ砲弾を0.35秒間隔で9発落とします。砲弾1発は半径3の範囲に108%のダメージを与えます。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>对前方半圆范围（射程4，角度180度）内的敌人造成150%伤害。</t>
+          <t>对前方半圆范围（射程4，角度180度）内的敌人造成270%伤害。</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -1805,7 +1805,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>判定范围从前方半圆变为360度圆形，可长按最多蓄力3秒。伤害根据蓄力时间从120%增至160%。</t>
+          <t>判定范围从前方半圆变为360度圆形，可长按最多蓄力3秒。伤害根据蓄力时间从270%增至470%。</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -1837,7 +1837,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>对前方直线范围（长度4，宽度2）内的敌人造成200%伤害。</t>
+          <t>对前方直线范围（长度4，宽度2）内的敌人造成360%伤害。</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -1852,7 +1852,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>判定范围缩小为长度2、宽度1，但伤害大幅提升至350%。</t>
+          <t>判定范围缩小为长度2、宽度1，但伤害大幅提升至630%。</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1931,22 +1931,22 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>向正面发射弹幕，命中敌人时对半径1范围造成120%伤害。改为使用最多6层层数管理，不再有冷却时间（每层4秒充能），连续发射间隔限制为1秒。</t>
+          <t>向正面发射弹幕，命中敌人时对半径1范围造成216%伤害。改为使用最多6层层数管理，不再有冷却时间（每层4秒充能），连续发射间隔限制为1秒。</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>消耗层数，立即命中一条长直线（长度12、宽度2）。每层消耗35点MP，MP不足时只消耗可支付的层数。每层伤害+50%（最多6层），无爆炸伤害。</t>
+          <t>消耗层数，立即命中一条长直线（长度12、宽度2）。每层消耗27点MP，MP不足时只消耗可支付的层数。每层伤害+50%（最多6层），无爆炸伤害。</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>消耗1层发射3发威力减弱的弹幕（伤害50%），间隔0.1秒连续发射。不会爆炸，只对命中的单个目标造成伤害。</t>
+          <t>消耗1层发射3发威力减弱的弹幕（伤害90%），间隔0.1秒连续发射。不会爆炸，只对命中的单个目标造成伤害。</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>消耗2层发射爆炸范围大幅扩大至3（基础的3倍）的扩展爆炸弹。伤害倍率也大幅提升至250%。</t>
+          <t>消耗2层发射爆炸范围大幅扩大至3（基础的3倍）的扩展爆炸弹。伤害倍率也大幅提升至450%。</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1978,7 +1978,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>朝光标位置（最大射程6）以抛物线投掷炸弹。接触敌人或落地后2秒，对半径3范围造成150%伤害。</t>
+          <t>朝光标位置（最大射程6）以抛物线投掷炸弹。接触敌人或落地后2秒，对半径3范围造成270%伤害。</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -2025,12 +2025,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>对前方扇形范围（射程5，角度90度）内的敌人造成100%伤害，随后朝光标反方向（后方）短距离后退（距离2）。</t>
+          <t>对前方扇形范围（射程5，角度90度）内的敌人造成180%伤害，随后朝光标反方向（后方）短距离后退（距离2）。</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>不再进行扇形攻击，而是在原位置放置诱饵。诱饵会在3秒后自动爆炸，对半径3范围造成100%伤害。</t>
+          <t>不再进行扇形攻击，而是在原位置放置诱饵。诱饵会在3秒后自动爆炸，对半径3范围造成180%伤害。</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -2072,7 +2072,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>对自身周围半径3范围内的敌人造成100%伤害，并在15秒内提升攻击力30%、攻击速度25%、移动速度15%、防御30%。</t>
+          <t>对自身周围半径3范围内的敌人造成180%伤害，并在15秒内提升攻击力30%、攻击速度25%、移动速度15%、防御30%。</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>施放时的爆炸伤害提升至400%，半径扩大至1.7倍。作为代价，强化效果持续时间缩短至5秒。</t>
+          <t>施放时的爆炸伤害提升至720%，半径扩大至1.7倍。作为代价，强化效果持续时间缩短至5秒。</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -2119,22 +2119,22 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>以光标位置为中心，对半径8的整个区域以0.5秒间隔轰炸3次，每次造成120%伤害。</t>
+          <t>以光标位置为中心，对半径8的整个区域以0.5秒间隔轰炸3次，每次造成216%伤害。</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>不再分多波轰炸，而是在施放0.5秒后对整个区域一次性造成450%伤害。</t>
+          <t>不再分多波轰炸，而是在施放0.5秒后对整个区域一次性造成810%伤害。</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>轰炸以1秒间隔进行4波，每波造成100%伤害。被命中的敌人在5秒内受到的所有伤害提升25%，再次命中时会叠加剩余时间。</t>
+          <t>轰炸以1秒间隔进行4波，每波造成180%伤害。被命中的敌人在5秒内受到的所有伤害提升25%，再次命中时会叠加剩余时间。</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>不再覆盖整个区域，而是以0.35秒间隔向范围内的随机位置投下9发炮弹。每发炮弹对半径3的范围造成60%伤害。</t>
+          <t>不再覆盖整个区域，而是以0.35秒间隔向范围内的随机位置投下9发炮弹。每发炮弹对半径3的范围造成108%伤害。</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
